--- a/samples/mock_280_import.xlsx
+++ b/samples/mock_280_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N281"/>
+  <dimension ref="A1:M281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,35 +454,30 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>CampGroup</t>
+          <t>BusTo</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>BusTo</t>
+          <t>BusBack</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>BusBack</t>
+          <t>RoomGroup</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>RoomGroup</t>
+          <t>Room</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>RoomNote</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>RoomNote</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -524,7 +519,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -532,17 +531,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>R001</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -580,7 +574,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -588,17 +586,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>R001</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -636,7 +629,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>Y</t>
@@ -644,17 +641,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>R001</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,7 +684,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -700,17 +696,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
           <t>R001</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -748,25 +739,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>R002</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -804,25 +794,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
           <t>R003</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -860,7 +849,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>N</t>
@@ -868,17 +861,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
           <t>R004</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -916,7 +904,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>N</t>
@@ -924,17 +916,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
           <t>R004</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -972,7 +959,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>N</t>
@@ -980,17 +971,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
           <t>R004</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1028,7 +1014,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1036,17 +1026,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
           <t>R005</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1084,7 +1069,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1092,17 +1081,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
           <t>R005</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1140,7 +1124,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1148,17 +1136,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
           <t>R005</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1196,7 +1179,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1204,17 +1191,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
           <t>R005</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1252,7 +1234,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>N</t>
@@ -1260,17 +1246,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
           <t>R006</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1308,7 +1289,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1316,17 +1301,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
           <t>R007</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1364,7 +1344,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1372,17 +1356,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
           <t>R007</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1420,7 +1399,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1428,17 +1411,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
           <t>R007</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1476,7 +1454,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1484,17 +1466,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
           <t>R007</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1532,7 +1509,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>N</t>
@@ -1540,17 +1521,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
           <t>R008</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1588,7 +1564,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>N</t>
@@ -1596,17 +1576,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
           <t>R008</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1644,7 +1619,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>N</t>
@@ -1652,17 +1631,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
           <t>R008</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1700,7 +1674,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>N</t>
@@ -1708,17 +1686,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
           <t>R008</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1756,7 +1729,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>N</t>
@@ -1764,17 +1741,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
           <t>R009</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1812,7 +1784,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>N</t>
@@ -1820,17 +1796,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
           <t>R009</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1868,7 +1839,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>N</t>
@@ -1876,17 +1851,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
           <t>R010</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1924,25 +1894,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
           <t>R011</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1980,25 +1949,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
           <t>R011</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2036,7 +2004,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2044,17 +2016,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
           <t>R012</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2092,7 +2059,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2100,17 +2071,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
           <t>R012</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2148,7 +2114,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2156,17 +2126,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
           <t>R012</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2204,7 +2169,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2212,17 +2181,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
           <t>R012</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2260,7 +2224,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>N</t>
@@ -2268,17 +2236,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
           <t>R013</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2316,7 +2279,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>N</t>
@@ -2324,17 +2291,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
           <t>R013</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2372,7 +2334,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>N</t>
@@ -2380,17 +2346,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
           <t>R013</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2428,7 +2389,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>N</t>
@@ -2436,17 +2401,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
           <t>R013</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2484,25 +2444,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
           <t>R014</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2540,25 +2499,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
           <t>R014</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2596,25 +2554,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
           <t>R014</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2652,25 +2609,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
           <t>R014</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2708,7 +2664,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2716,17 +2676,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
           <t>R015</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2764,7 +2719,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2772,17 +2731,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
           <t>R015</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2820,7 +2774,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>N</t>
@@ -2828,17 +2786,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
           <t>R016</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2876,7 +2829,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>N</t>
@@ -2884,17 +2841,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
           <t>R016</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2932,7 +2884,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>N</t>
@@ -2940,17 +2896,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
           <t>R017</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2988,25 +2939,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
           <t>R018</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3044,25 +2994,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
           <t>R019</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3100,25 +3049,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
           <t>R019</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3156,25 +3104,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
           <t>R019</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3212,25 +3159,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
           <t>R019</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3268,25 +3214,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
           <t>R020</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3324,25 +3269,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
           <t>R020</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3380,25 +3324,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
           <t>R020</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3436,25 +3379,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
           <t>R020</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3492,7 +3434,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>N</t>
@@ -3500,17 +3446,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
           <t>R021</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3548,7 +3489,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>N</t>
@@ -3556,17 +3501,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
           <t>R021</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3604,7 +3544,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3612,17 +3556,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
           <t>R022</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3660,25 +3599,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
           <t>R023</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3716,25 +3654,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
           <t>R023</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3772,25 +3709,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
           <t>R023</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3828,25 +3764,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
           <t>R023</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3884,25 +3819,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
           <t>R024</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3940,25 +3874,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
           <t>R024</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3996,25 +3929,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
           <t>R024</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4052,25 +3984,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
           <t>R024</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4108,25 +4039,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
           <t>R025</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4164,25 +4094,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
           <t>R025</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4220,25 +4149,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
           <t>R025</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4276,25 +4204,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
           <t>R026</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4332,25 +4259,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
           <t>R027</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4388,25 +4314,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
           <t>R027</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4444,25 +4369,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
           <t>R028</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4500,25 +4424,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
           <t>R028</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4556,25 +4479,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
           <t>R029</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4612,25 +4534,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
           <t>R029</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4668,25 +4589,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
           <t>R029</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4724,25 +4644,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
           <t>R029</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4780,25 +4699,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
           <t>R030</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4836,25 +4754,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
           <t>R030</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4892,25 +4809,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
           <t>R030</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4948,25 +4864,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
           <t>R030</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5004,25 +4919,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
           <t>R031</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5060,25 +4974,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
           <t>R031</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5116,25 +5029,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
           <t>R031</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5172,7 +5084,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>N</t>
@@ -5180,17 +5096,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
           <t>R032</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5228,7 +5139,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>N</t>
@@ -5236,17 +5151,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
           <t>R032</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5284,7 +5194,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>N</t>
@@ -5292,17 +5206,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
           <t>R032</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5340,7 +5249,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>N</t>
@@ -5348,17 +5261,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
           <t>R032</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5396,25 +5304,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
           <t>R033</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5452,25 +5359,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
           <t>R033</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5508,25 +5414,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
           <t>R034</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5564,25 +5469,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
           <t>R034</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5620,25 +5524,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
           <t>R034</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5676,25 +5579,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
           <t>R035</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5732,25 +5634,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
           <t>R035</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5788,25 +5689,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
           <t>R035</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5844,7 +5744,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5852,17 +5756,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
           <t>R036</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5900,7 +5799,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5908,17 +5811,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
           <t>R036</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5956,7 +5854,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5964,17 +5866,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
           <t>R036</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6012,7 +5909,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>N</t>
@@ -6020,17 +5921,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
           <t>R037</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6068,7 +5964,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>N</t>
@@ -6076,17 +5976,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
           <t>R037</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6124,25 +6019,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
           <t>R038</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6180,25 +6074,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
           <t>R038</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6236,25 +6129,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
           <t>R038</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6292,25 +6184,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
           <t>R039</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6348,25 +6239,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
           <t>R039</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6404,25 +6294,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
           <t>R039</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6460,25 +6349,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
           <t>R039</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6516,25 +6404,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
           <t>R040</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6572,25 +6459,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
           <t>R040</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6628,25 +6514,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
           <t>R040</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6684,25 +6569,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
           <t>R040</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6740,7 +6624,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6748,17 +6636,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
           <t>R041</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6796,7 +6679,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6804,17 +6691,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
           <t>R041</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6852,25 +6734,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
           <t>R042</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6908,25 +6789,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
           <t>R042</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6964,25 +6844,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
           <t>R042</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7020,25 +6899,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
           <t>R042</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7076,7 +6954,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7084,17 +6966,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
           <t>R043</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7132,7 +7009,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7140,17 +7021,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
           <t>R043</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7188,7 +7064,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7196,17 +7076,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
           <t>R043</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7244,7 +7119,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7252,17 +7131,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
           <t>R043</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7300,25 +7174,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
           <t>R044</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7356,25 +7229,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
           <t>R044</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7412,7 +7284,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7420,17 +7296,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
           <t>R045</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7468,7 +7339,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7476,17 +7351,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
           <t>R045</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7524,7 +7394,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7532,17 +7406,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
           <t>R045</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7580,25 +7449,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
           <t>R046</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7636,25 +7504,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
           <t>R047</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7692,25 +7559,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
           <t>R047</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7748,7 +7614,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7756,17 +7626,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
           <t>R048</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7804,7 +7669,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7812,17 +7681,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
           <t>R048</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7860,7 +7724,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7868,17 +7736,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
           <t>R049</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7916,7 +7779,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
           <t>N</t>
@@ -7924,17 +7791,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
           <t>R050</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7972,7 +7834,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
           <t>N</t>
@@ -7980,17 +7846,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
           <t>R050</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8028,7 +7889,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>N</t>
@@ -8036,17 +7901,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
           <t>R050</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8084,7 +7944,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>N</t>
@@ -8092,17 +7956,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
           <t>R050</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8140,25 +7999,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
           <t>R051</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8196,25 +8054,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
           <t>R051</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8252,25 +8109,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
           <t>R051</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8308,25 +8164,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
           <t>R051</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8364,7 +8219,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8372,17 +8231,12 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
           <t>R052</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8420,7 +8274,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8428,17 +8286,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
           <t>R052</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8476,25 +8329,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
           <t>R053</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8532,25 +8384,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
           <t>R053</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8588,7 +8439,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8596,17 +8451,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
           <t>R054</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8644,25 +8494,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
           <t>R055</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8700,7 +8549,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr">
         <is>
           <t>N</t>
@@ -8708,17 +8561,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
           <t>R056</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8756,25 +8604,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
           <t>R057</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8812,25 +8659,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
           <t>R057</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8868,25 +8714,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
           <t>R057</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8924,25 +8769,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
           <t>R057</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8980,7 +8824,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
           <t>N</t>
@@ -8988,17 +8836,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
           <t>R058</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9036,7 +8879,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I154" t="inlineStr">
         <is>
           <t>N</t>
@@ -9044,17 +8891,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
           <t>R058</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9092,7 +8934,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr">
         <is>
           <t>N</t>
@@ -9100,17 +8946,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
           <t>R058</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9148,7 +8989,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I156" t="inlineStr">
         <is>
           <t>N</t>
@@ -9156,17 +9001,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
           <t>R058</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9204,25 +9044,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
           <t>R059</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9260,25 +9099,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
           <t>R059</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9316,25 +9154,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
           <t>R059</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9372,25 +9209,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
           <t>R059</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9428,7 +9264,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I161" t="inlineStr">
         <is>
           <t>N</t>
@@ -9436,17 +9276,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
           <t>R060</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9484,7 +9319,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I162" t="inlineStr">
         <is>
           <t>N</t>
@@ -9492,17 +9331,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
           <t>R060</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9540,25 +9374,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
           <t>R061</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9596,25 +9429,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
           <t>R061</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9652,7 +9484,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I165" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9660,17 +9496,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
           <t>R062</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9708,7 +9539,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I166" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9716,17 +9551,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
           <t>R062</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9764,25 +9594,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
           <t>R063</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9820,25 +9649,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
           <t>R063</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9876,25 +9704,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
           <t>R063</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9932,25 +9759,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
           <t>R063</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9988,25 +9814,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
           <t>R064</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10044,25 +9869,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
           <t>R064</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10100,25 +9924,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
           <t>R064</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10156,7 +9979,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I174" t="inlineStr">
         <is>
           <t>N</t>
@@ -10164,17 +9991,12 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
           <t>R065</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10212,7 +10034,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I175" t="inlineStr">
         <is>
           <t>N</t>
@@ -10220,17 +10046,12 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
           <t>R065</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10268,7 +10089,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I176" t="inlineStr">
         <is>
           <t>N</t>
@@ -10276,17 +10101,12 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
           <t>R065</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10324,7 +10144,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr">
         <is>
           <t>N</t>
@@ -10332,17 +10156,12 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
           <t>R065</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10380,7 +10199,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
           <t>N</t>
@@ -10388,17 +10211,12 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
           <t>R066</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10436,7 +10254,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr">
         <is>
           <t>N</t>
@@ -10444,17 +10266,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
           <t>R066</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10492,7 +10309,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr">
         <is>
           <t>N</t>
@@ -10500,17 +10321,12 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
           <t>R066</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10548,7 +10364,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I181" t="inlineStr">
         <is>
           <t>N</t>
@@ -10556,17 +10376,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
           <t>R066</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10604,7 +10419,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr">
         <is>
           <t>N</t>
@@ -10612,17 +10431,12 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
           <t>R067</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10660,7 +10474,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I183" t="inlineStr">
         <is>
           <t>N</t>
@@ -10668,17 +10486,12 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
           <t>R067</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10716,7 +10529,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I184" t="inlineStr">
         <is>
           <t>N</t>
@@ -10724,17 +10541,12 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
           <t>R067</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10772,7 +10584,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I185" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10780,17 +10596,12 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
           <t>R068</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10828,7 +10639,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I186" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10836,17 +10651,12 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
           <t>R069</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10884,7 +10694,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I187" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10892,17 +10706,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
           <t>R069</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10940,7 +10749,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I188" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10948,17 +10761,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
           <t>R069</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10996,7 +10804,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I189" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11004,17 +10816,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
           <t>R069</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11052,7 +10859,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I190" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11060,17 +10871,12 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
           <t>R070</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11108,7 +10914,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I191" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11116,17 +10926,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
           <t>R070</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11164,7 +10969,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11172,17 +10981,12 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
           <t>R070</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11220,7 +11024,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I193" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11228,17 +11036,12 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
           <t>R070</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11276,25 +11079,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
           <t>R071</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11332,25 +11134,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
           <t>R071</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11388,25 +11189,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
           <t>R072</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11444,25 +11244,24 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
           <t>R072</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11500,7 +11299,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I198" t="inlineStr">
         <is>
           <t>N</t>
@@ -11508,17 +11311,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
           <t>R073</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11556,7 +11354,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I199" t="inlineStr">
         <is>
           <t>N</t>
@@ -11564,17 +11366,12 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
           <t>R073</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11612,25 +11409,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
           <t>R074</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11668,25 +11464,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
           <t>R074</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11724,25 +11519,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
           <t>R074</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11780,25 +11574,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
           <t>R075</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11836,25 +11629,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
           <t>R075</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11892,25 +11684,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
           <t>R075</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11948,25 +11739,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
           <t>R075</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12004,25 +11794,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
           <t>R076</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12060,25 +11849,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
           <t>R076</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12116,25 +11904,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
           <t>R077</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12172,25 +11959,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
           <t>R077</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12228,25 +12014,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
           <t>R077</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12284,25 +12069,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
           <t>R077</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12340,7 +12124,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
         <is>
           <t>N</t>
@@ -12348,17 +12136,12 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
           <t>R078</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12396,7 +12179,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I214" t="inlineStr">
         <is>
           <t>N</t>
@@ -12404,17 +12191,12 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
           <t>R078</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12452,7 +12234,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr">
         <is>
           <t>N</t>
@@ -12460,17 +12246,12 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
           <t>R078</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12508,7 +12289,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I216" t="inlineStr">
         <is>
           <t>N</t>
@@ -12516,17 +12301,12 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
           <t>R079</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12564,7 +12344,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I217" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12572,17 +12356,12 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
           <t>R080</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12620,7 +12399,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I218" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12628,17 +12411,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
           <t>R080</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12676,7 +12454,11 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I219" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12684,17 +12466,12 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
           <t>R080</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12732,25 +12509,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
           <t>R081</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12788,25 +12564,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
           <t>R081</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12844,25 +12619,24 @@
           <t>姐妹组</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
           <t>R081</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12900,7 +12674,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I223" t="inlineStr">
         <is>
           <t>N</t>
@@ -12908,17 +12686,12 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
           <t>R082</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12956,7 +12729,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I224" t="inlineStr">
         <is>
           <t>N</t>
@@ -12964,17 +12741,12 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
           <t>R082</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13012,7 +12784,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I225" t="inlineStr">
         <is>
           <t>N</t>
@@ -13020,17 +12796,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
           <t>R083</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13068,7 +12839,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I226" t="inlineStr">
         <is>
           <t>N</t>
@@ -13076,17 +12851,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
           <t>R083</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13124,7 +12894,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr">
         <is>
           <t>N</t>
@@ -13132,17 +12906,12 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
           <t>R083</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13180,25 +12949,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
           <t>R084</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13236,25 +13004,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
           <t>R084</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13292,25 +13059,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
           <t>R085</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13348,25 +13114,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
           <t>R085</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13404,25 +13169,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
           <t>R085</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13460,25 +13224,24 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
           <t>R085</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13516,25 +13279,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
           <t>R086</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13572,25 +13334,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
           <t>R086</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13628,25 +13389,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
           <t>R087</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13684,25 +13444,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
           <t>R087</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13740,25 +13499,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
           <t>R087</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13796,7 +13554,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I239" t="inlineStr">
         <is>
           <t>N</t>
@@ -13804,17 +13566,12 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
           <t>R088</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13852,7 +13609,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I240" t="inlineStr">
         <is>
           <t>N</t>
@@ -13860,17 +13621,12 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
           <t>R088</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13908,7 +13664,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I241" t="inlineStr">
         <is>
           <t>N</t>
@@ -13916,17 +13676,12 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
           <t>R088</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13964,7 +13719,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I242" t="inlineStr">
         <is>
           <t>N</t>
@@ -13972,17 +13731,12 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
           <t>R088</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14020,25 +13774,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
           <t>R089</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14076,25 +13829,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
           <t>R089</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14132,25 +13884,24 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
           <t>R089</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14188,7 +13939,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr">
         <is>
           <t>N</t>
@@ -14196,17 +13951,12 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
           <t>R090</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14244,7 +13994,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I247" t="inlineStr">
         <is>
           <t>N</t>
@@ -14252,17 +14006,12 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
           <t>R090</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14300,25 +14049,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
           <t>R091</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14356,25 +14104,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
           <t>R091</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14412,25 +14159,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
           <t>R091</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14468,25 +14214,24 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
           <t>R091</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14524,25 +14269,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
           <t>R092</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14580,25 +14324,24 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
           <t>R092</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14636,7 +14379,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I254" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14644,17 +14391,12 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
           <t>R093</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14692,7 +14434,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I255" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14700,17 +14446,12 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
           <t>R093</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14748,7 +14489,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I256" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14756,17 +14501,12 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
           <t>R093</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14804,7 +14544,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I257" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14812,17 +14556,12 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
           <t>R093</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14860,7 +14599,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I258" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14868,17 +14611,12 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
           <t>R094</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14916,7 +14654,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I259" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14924,17 +14666,12 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
           <t>R094</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14972,7 +14709,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I260" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14980,17 +14721,12 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
           <t>R095</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15028,7 +14764,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I261" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15036,17 +14776,12 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
           <t>R095</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15084,7 +14819,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I262" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15092,17 +14831,12 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
           <t>R095</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15140,7 +14874,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I263" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15148,17 +14886,12 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
           <t>R096</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15196,7 +14929,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I264" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15204,17 +14941,12 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
           <t>R096</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15252,7 +14984,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I265" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15260,17 +14996,12 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
           <t>R097</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
       <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15308,7 +15039,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I266" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15316,17 +15051,12 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
           <t>R097</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15364,7 +15094,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I267" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15372,17 +15106,12 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
           <t>R097</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15420,7 +15149,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I268" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15428,17 +15161,12 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
           <t>R098</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15476,7 +15204,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I269" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15484,17 +15216,12 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
           <t>R098</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15532,7 +15259,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I270" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15540,17 +15271,12 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
           <t>R098</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15588,7 +15314,11 @@
           <t>长青组</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I271" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15596,17 +15326,12 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
           <t>R098</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15644,7 +15369,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I272" t="inlineStr">
         <is>
           <t>N</t>
@@ -15652,17 +15381,12 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
           <t>R099</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15700,7 +15424,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I273" t="inlineStr">
         <is>
           <t>N</t>
@@ -15708,17 +15436,12 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
           <t>R099</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15756,7 +15479,11 @@
           <t>青年组</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I274" t="inlineStr">
         <is>
           <t>N</t>
@@ -15764,17 +15491,12 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
           <t>R099</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15812,7 +15534,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I275" t="inlineStr">
         <is>
           <t>N</t>
@@ -15820,17 +15546,12 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
           <t>R100</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15868,7 +15589,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I276" t="inlineStr">
         <is>
           <t>N</t>
@@ -15876,17 +15601,12 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
           <t>R100</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15924,7 +15644,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I277" t="inlineStr">
         <is>
           <t>N</t>
@@ -15932,17 +15656,12 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
           <t>R100</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15980,7 +15699,11 @@
           <t>弟兄组</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I278" t="inlineStr">
         <is>
           <t>N</t>
@@ -15988,17 +15711,12 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
           <t>R100</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16036,7 +15754,11 @@
           <t>少年组</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I279" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16044,17 +15766,12 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
           <t>R101</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16092,7 +15809,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I280" t="inlineStr">
         <is>
           <t>N</t>
@@ -16100,17 +15821,12 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
           <t>R102</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16148,7 +15864,11 @@
           <t>夫妻组</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I281" t="inlineStr">
         <is>
           <t>N</t>
@@ -16156,17 +15876,12 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
           <t>R102</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
